--- a/Documentation/DOC_ExG_shield_unipolar/Bill of Materials-ExG_shield(Unipolar_supply).xlsx
+++ b/Documentation/DOC_ExG_shield_unipolar/Bill of Materials-ExG_shield(Unipolar_supply).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s-fre\Github\biogap-exg-shield\ExG_shield_pcb\Project Outputs for ExG_shield\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s-fre\Github\biogap_public\submodules\sensei-exg-shield\Documentation\DOC_ExG_shield_unipolar\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{930219C6-8C23-4319-A2FA-F2CFE5EDF317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E2038CD-7FA9-4400-91EC-A2D52268C1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="12645" xr2:uid="{02E636B8-D280-4BDD-A704-24F1E45DDC7C}"/>
+    <workbookView xWindow="34155" yWindow="4050" windowWidth="21600" windowHeight="12450" xr2:uid="{44DD1E36-3AFD-4E88-B7A0-01BCF7EF1C22}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-ExG_shield(Un" sheetId="1" r:id="rId1"/>
@@ -32,12 +32,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="71">
   <si>
     <t>Comment</t>
   </si>
@@ -48,12 +51,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>Footprint</t>
-  </si>
-  <si>
-    <t>LibRef</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -63,13 +60,7 @@
     <t>Cap Ceramic 100nF 25V X5R ±10% SMD 0402 +85°C Paper T/R</t>
   </si>
   <si>
-    <t>C1, C3, C4, C7, C10, C15, C17, C18, C22, C25, C32, C33, C34, C40, C41</t>
-  </si>
-  <si>
-    <t>FP-CL278-IPC_C</t>
-  </si>
-  <si>
-    <t>CMP-13271-000728-1</t>
+    <t>C1, C3, C4, C7, C10, C15, C17, C18, C22, C25, C32, C33, C34, C40</t>
   </si>
   <si>
     <t>CL05A105KP5NNNC</t>
@@ -81,12 +72,6 @@
     <t>C2, C5, C6, C9, C11, C12, C16, C19, C20, C24, C26, C27, C39, C42</t>
   </si>
   <si>
-    <t>FP-CL511-IPC_C</t>
-  </si>
-  <si>
-    <t>CMP-13271-001936-1</t>
-  </si>
-  <si>
     <t>CL05A106MP8NUB8</t>
   </si>
   <si>
@@ -96,27 +81,12 @@
     <t>C8, C23, C31</t>
   </si>
   <si>
-    <t>FP-CL07-IPC_C</t>
-  </si>
-  <si>
-    <t>CMP-13271-002778-1</t>
-  </si>
-  <si>
-    <t>04025C102KAT2A</t>
-  </si>
-  <si>
     <t>General Purpose Ceramic Capacitor, 0402, 1nF, 10%, X7R, 15%, 50V</t>
   </si>
   <si>
     <t>C13, C28</t>
   </si>
   <si>
-    <t>FP-0402-L_1_0_1-W_0_5_0_1-IPC_B</t>
-  </si>
-  <si>
-    <t>CMP-2008-02699-2</t>
-  </si>
-  <si>
     <t>CL05A226MQ5QUNC</t>
   </si>
   <si>
@@ -126,24 +96,12 @@
     <t>C14, C29</t>
   </si>
   <si>
-    <t>FP-CL746-IPC_C</t>
-  </si>
-  <si>
-    <t>CMP-13271-000286-1</t>
-  </si>
-  <si>
     <t>GRM155R71H152KA01D</t>
   </si>
   <si>
     <t>C21</t>
   </si>
   <si>
-    <t>CAPC1005X55X25NL05T10</t>
-  </si>
-  <si>
-    <t>CMP-2008-04642-1</t>
-  </si>
-  <si>
     <t>CGA2B3X7R1V103K050BB</t>
   </si>
   <si>
@@ -153,24 +111,12 @@
     <t>C30</t>
   </si>
   <si>
-    <t>FP-CGA2B-MFG</t>
-  </si>
-  <si>
-    <t>CMP-08246-000497-1</t>
-  </si>
-  <si>
-    <t>DF52-2S-0.8H_21_</t>
-  </si>
-  <si>
     <t>Connector</t>
   </si>
   <si>
     <t>J1, J2, J7, J8, J9, J10, J11, J12, J13, J14, J15, J16, J17, J18, J19, J20, J21, J22, J23, J25</t>
   </si>
   <si>
-    <t>DF522S08H21</t>
-  </si>
-  <si>
     <t>DF40HC(2.5)-40DS-0.4V(51)</t>
   </si>
   <si>
@@ -180,12 +126,6 @@
     <t>J3</t>
   </si>
   <si>
-    <t>DF40HC3040DS04V51</t>
-  </si>
-  <si>
-    <t>DF40HC(3.0)-40DS-0.4V(51)</t>
-  </si>
-  <si>
     <t>DF40HC(2.5)-50DS-0.4V(51)</t>
   </si>
   <si>
@@ -195,12 +135,6 @@
     <t>J4</t>
   </si>
   <si>
-    <t>DF40HC3050DS04V51</t>
-  </si>
-  <si>
-    <t>DF40HC(3.0)-50DS-0.4V(51)</t>
-  </si>
-  <si>
     <t>DF40C-40DP-0.4V(51)</t>
   </si>
   <si>
@@ -210,9 +144,6 @@
     <t>J5</t>
   </si>
   <si>
-    <t>FP-DF40C-40DP-0_4V_51-MFG</t>
-  </si>
-  <si>
     <t>DF40C-50DP-0.4V(51)</t>
   </si>
   <si>
@@ -222,30 +153,18 @@
     <t>J6</t>
   </si>
   <si>
-    <t>CONN_COMBI_50P</t>
-  </si>
-  <si>
     <t>505070-4222</t>
   </si>
   <si>
     <t>J24</t>
   </si>
   <si>
-    <t>5050704222</t>
-  </si>
-  <si>
-    <t>PMSS3906</t>
-  </si>
-  <si>
     <t>PNP Switching Transistor</t>
   </si>
   <si>
     <t>Q1</t>
   </si>
   <si>
-    <t>SOT323_N</t>
-  </si>
-  <si>
     <t>MCS04020C1004FE000</t>
   </si>
   <si>
@@ -255,12 +174,6 @@
     <t>R1</t>
   </si>
   <si>
-    <t>FP-MCS0402-IPC_C</t>
-  </si>
-  <si>
-    <t>CMP-02407-000443-1</t>
-  </si>
-  <si>
     <t>RC0402FR-070RL</t>
   </si>
   <si>
@@ -270,12 +183,6 @@
     <t>R4, R9, R14</t>
   </si>
   <si>
-    <t>FP-RC0402-0_4-IPC_A</t>
-  </si>
-  <si>
-    <t>CMP-2002-07342-2</t>
-  </si>
-  <si>
     <t>RT0402FRE074K7L</t>
   </si>
   <si>
@@ -285,12 +192,6 @@
     <t>R5, R6, R7, R15, R16, R17, R18, R19, R20, R21, R22, R23, R24, R25, R26, R27, R28, R29, R30, R31</t>
   </si>
   <si>
-    <t>FP-RT0402-MFG</t>
-  </si>
-  <si>
-    <t>CMP-2002-02901-2</t>
-  </si>
-  <si>
     <t>RR0510P-563-D</t>
   </si>
   <si>
@@ -300,18 +201,9 @@
     <t>R8</t>
   </si>
   <si>
-    <t>FP-RR0510-MFG</t>
-  </si>
-  <si>
-    <t>CMP-2002-01632-2</t>
-  </si>
-  <si>
     <t>R10, R11, R12, R33</t>
   </si>
   <si>
-    <t>FP-RC0402-0_4-IPC_C</t>
-  </si>
-  <si>
     <t>ADS1298RIZXGT</t>
   </si>
   <si>
@@ -321,12 +213,6 @@
     <t>U1, U2</t>
   </si>
   <si>
-    <t>TI-ZXG64</t>
-  </si>
-  <si>
-    <t>CMP-0003-00996-1</t>
-  </si>
-  <si>
     <t>ISL21080CIH320Z-TK</t>
   </si>
   <si>
@@ -336,12 +222,6 @@
     <t>U3</t>
   </si>
   <si>
-    <t>FP-P3_064A-IPC_C</t>
-  </si>
-  <si>
-    <t>CMP-13559-000004-1</t>
-  </si>
-  <si>
     <t>TPS22916CYFPR</t>
   </si>
   <si>
@@ -351,9 +231,6 @@
     <t>U6</t>
   </si>
   <si>
-    <t>BGA4C40P2X2_78X78X50</t>
-  </si>
-  <si>
     <t>SIT8021AC-J3-18S-2.048000</t>
   </si>
   <si>
@@ -363,10 +240,19 @@
     <t>Y1</t>
   </si>
   <si>
-    <t>FP-SiT8021-MFG</t>
-  </si>
-  <si>
-    <t>CMP-25159-259502-1</t>
+    <t>04025C102KAT2A-62</t>
+  </si>
+  <si>
+    <t>DF52-2S-0.8H</t>
+  </si>
+  <si>
+    <t>PMSS3906,115</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>We will send this part</t>
   </si>
 </sst>
 </file>
@@ -382,7 +268,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,8 +281,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -419,16 +311,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -742,14 +649,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FB2475-CD05-463E-A8AA-7D4A0630FAC6}">
-  <dimension ref="A1:F24"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34B576E7-A5FD-43C3-85A8-685A6E92992F}">
+  <dimension ref="A1:E24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="19.7109375" customWidth="1"/>
+    <col min="1" max="4" width="19.7109375" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -762,473 +670,335 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="1">
+        <v>14</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="1">
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="B14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="1">
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="D20" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="B23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="D24" s="7">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>70</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="1">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F20" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>